--- a/mock_e2e_project/7. Chronology/Slave/Ladder_Chronology.xlsx
+++ b/mock_e2e_project/7. Chronology/Slave/Ladder_Chronology.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$P$20</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -46,8 +48,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -411,10 +419,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="8.65" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="8.65" customWidth="1" min="7" max="7"/>
+    <col width="6.75" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11.5" customWidth="1" min="10" max="10"/>
+    <col width="11.5" customWidth="1" min="11" max="11"/>
+    <col width="9.6" customWidth="1" min="12" max="12"/>
+    <col width="11.5" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="7.7" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1"/>
     <row r="2"/>
@@ -429,7 +455,7 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
-    <row r="14">
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>Serial No.</t>
@@ -512,73 +538,84 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Instructions</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>C:\Users\SM 464\Desktop\Operational Package Validator\ProjectValidator\mock_e2e_project\2. Bin File\Slave\FW_V2.01.bin</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>FW_V2.01.bin</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>V2.01</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Slave</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>FW</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>V2.01</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>05/08/2026</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
     </row>
-    <row r="17"/>
-    <row r="19">
-      <c r="B19" t="inlineStr">
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Footer Text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B15:P15"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B16:P16"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="1" header="0.3" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>